--- a/dataset/construct/dataset_splits/data_size/10_percent/lmu/fold4.xlsx
+++ b/dataset/construct/dataset_splits/data_size/10_percent/lmu/fold4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN15"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,185 +446,170 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>DM</t>
+          <t>BMI</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>BMI</t>
+          <t>AFPRE</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>CABGPRE</t>
+          <t>LVEFPRE</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>AFPRE</t>
+          <t>PREDILATION</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>LVEFPRE</t>
+          <t>CT_ValScNCC</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>NTPROBNPPRE</t>
+          <t>CT_ValScRCC</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>PREDILATION</t>
+          <t>CT_ValScLCC</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScNCC</t>
+          <t>CT_ValvScTot</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScRCC</t>
+          <t>CT_AnnScNCC</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValScLCC</t>
+          <t>CT_AnnScRCC</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>CT_ValvScTot</t>
+          <t>CT_AnnScLCC</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScNCC</t>
+          <t>CT_AnnScTot</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScRCC</t>
+          <t>CT_LVOTScNCC</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScLCC</t>
+          <t>CT_LVOTScRCC</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnScTot</t>
+          <t>CT_LVOTScLCC</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScNCC</t>
+          <t>CT_LVOTScTot</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScRCC</t>
+          <t>SEX</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScLCC</t>
+          <t>CT_AnnMean</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>CT_LVOTScTot</t>
+          <t>ECC_INDEX</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>SEX</t>
+          <t>CT_Peri_Deri</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>CT_AnnMean</t>
+          <t>CT_Area_Deri</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>ECC_INDEX</t>
+          <t>nyha2</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>CT_Peri_Deri</t>
+          <t>nyha3</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>CT_Area_Deri</t>
+          <t>nyha4</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>nyha2</t>
+          <t>model1</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>nyha3</t>
+          <t>model2</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>nyha4</t>
+          <t>model3</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>model1</t>
+          <t>model4</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>model2</t>
+          <t>model7</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>model3</t>
+          <t>model8</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>model4</t>
+          <t>brand2</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>model7</t>
+          <t>brand8</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>model8</t>
+          <t>QRSADM</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
-        <is>
-          <t>brand2</t>
-        </is>
-      </c>
-      <c r="AL1" s="1" t="inlineStr">
-        <is>
-          <t>brand8</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>QRSADM</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>PQADM</t>
         </is>
@@ -632,7 +617,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>54391258</v>
+        <v>51322415</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -640,71 +625,85 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>83.09377138945931</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>86.072553045859</v>
+      </c>
+      <c r="D2" t="n">
+        <v>20.1234567901235</v>
+      </c>
       <c r="E2" t="n">
-        <v>23.5078053259871</v>
-      </c>
-      <c r="F2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>60</v>
+      </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>55</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
+        <v>600</v>
+      </c>
+      <c r="I2" t="n">
+        <v>419</v>
+      </c>
       <c r="J2" t="n">
-        <v>1</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+        <v>611</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1630</v>
+      </c>
+      <c r="L2" t="n">
+        <v>600</v>
+      </c>
+      <c r="M2" t="n">
+        <v>359</v>
+      </c>
+      <c r="N2" t="n">
+        <v>604</v>
+      </c>
       <c r="O2" t="n">
-        <v>131</v>
+        <v>1563</v>
       </c>
       <c r="P2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>405</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>29</v>
+        <v>27.1</v>
       </c>
       <c r="V2" t="n">
-        <v>29</v>
+        <v>0.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>27.43831218904276</v>
       </c>
       <c r="X2" t="n">
-        <v>27.2</v>
+        <v>26.41226886430614</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>575</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>0</v>
@@ -725,24 +724,15 @@
         <v>0</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>176</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>132</v>
+        <v>145</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>54143780</v>
+        <v>53531320</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -750,67 +740,79 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>79.5564681724846</v>
+        <v>82.072553045859</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>23.4375</v>
       </c>
       <c r="E3" t="n">
-        <v>22.4600343506408</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>45</v>
+      </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>69</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
+        <v>182</v>
+      </c>
+      <c r="I3" t="n">
+        <v>337</v>
+      </c>
       <c r="J3" t="n">
-        <v>1</v>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="K3" t="n">
+        <v>663</v>
+      </c>
+      <c r="L3" t="n">
+        <v>175</v>
+      </c>
+      <c r="M3" t="n">
+        <v>276</v>
+      </c>
+      <c r="N3" t="n">
+        <v>93</v>
+      </c>
       <c r="O3" t="n">
-        <v>519</v>
+        <v>544</v>
       </c>
       <c r="P3" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>808</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1670</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>24.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>25.91042473536056</v>
       </c>
       <c r="X3" t="n">
-        <v>27.7</v>
+        <v>24.89604407083738</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.11</v>
+        <v>1</v>
       </c>
       <c r="Z3" t="n">
-        <v>88.90000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
-        <v>621.5</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -837,24 +839,15 @@
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>144</v>
       </c>
       <c r="AK3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>187</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>160</v>
+        <v>136</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>54682114</v>
+        <v>55219139</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -862,77 +855,83 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>80.50376454483229</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>88.8870636550308</v>
+      </c>
+      <c r="D4" t="n">
+        <v>29.6679712157556</v>
+      </c>
       <c r="E4" t="n">
-        <v>25.8264462809917</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>40</v>
+      </c>
       <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>55</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="n">
-        <v>1</v>
-      </c>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="L4" t="n">
+        <v>203</v>
+      </c>
+      <c r="M4" t="n">
+        <v>146</v>
+      </c>
+      <c r="N4" t="n">
+        <v>130</v>
+      </c>
       <c r="O4" t="n">
-        <v>1335</v>
+        <v>479</v>
       </c>
       <c r="P4" t="n">
-        <v>839</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>670</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2844</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>16</v>
+        <v>28</v>
       </c>
       <c r="V4" t="n">
-        <v>16</v>
+        <v>0.35</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>29.3481715061455</v>
       </c>
       <c r="X4" t="n">
-        <v>27.9</v>
+        <v>27.96241056171416</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>94.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>620.9</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
       </c>
       <c r="AC4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD4" t="n">
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
@@ -947,24 +946,15 @@
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>178</v>
       </c>
       <c r="AK4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>195</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>152</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55151543</v>
+        <v>52427931</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -972,77 +962,91 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>90.1026694045175</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>73.3442847364819</v>
+      </c>
+      <c r="D5" t="n">
+        <v>25.7370814149675</v>
+      </c>
       <c r="E5" t="n">
-        <v>25.1428571428571</v>
-      </c>
-      <c r="F5" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>45</v>
+      </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>55</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
+        <v>451</v>
+      </c>
+      <c r="I5" t="n">
+        <v>420</v>
+      </c>
       <c r="J5" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>192</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1063</v>
+      </c>
+      <c r="L5" t="n">
+        <v>437</v>
+      </c>
+      <c r="M5" t="n">
+        <v>183</v>
+      </c>
+      <c r="N5" t="n">
+        <v>161</v>
+      </c>
       <c r="O5" t="n">
-        <v>476</v>
+        <v>781</v>
       </c>
       <c r="P5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>310</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>986</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>26.1</v>
       </c>
       <c r="V5" t="n">
-        <v>157</v>
+        <v>0.24</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>26.57887549634652</v>
       </c>
       <c r="X5" t="n">
-        <v>24.1</v>
+        <v>25.53230594569169</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.35</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>78.5</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>428.5</v>
+        <v>1</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
@@ -1057,24 +1061,15 @@
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>129</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>110</v>
+        <v>316</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53286546</v>
+        <v>54617532</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -1082,85 +1077,83 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>87.1622176591376</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>88.7994524298426</v>
+      </c>
+      <c r="D6" t="n">
+        <v>24.1632653061225</v>
+      </c>
       <c r="E6" t="n">
-        <v>27.1020408163265</v>
-      </c>
-      <c r="F6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>33</v>
+      </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
-      <c r="H6" t="n">
-        <v>55</v>
-      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" t="n">
-        <v>110</v>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="n">
-        <v>169</v>
+        <v>199</v>
       </c>
       <c r="M6" t="n">
-        <v>142</v>
+        <v>184</v>
       </c>
       <c r="N6" t="n">
-        <v>420</v>
+        <v>264</v>
       </c>
       <c r="O6" t="n">
-        <v>110</v>
+        <v>647</v>
       </c>
       <c r="P6" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>373</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>228</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>197</v>
+        <v>27.7</v>
       </c>
       <c r="V6" t="n">
-        <v>425</v>
+        <v>0.26</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>28.87070667686982</v>
       </c>
       <c r="X6" t="n">
-        <v>25.9</v>
+        <v>28.11453555319008</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>83.7</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>489.4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -1169,26 +1162,21 @@
         <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
+        <v>172</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>54503794</v>
+        <v>54306970</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -1196,109 +1184,106 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>84.3969883641342</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>70.92676249144419</v>
+      </c>
+      <c r="D7" t="n">
+        <v>22.7244034844085</v>
+      </c>
       <c r="E7" t="n">
-        <v>24.6755002704164</v>
-      </c>
-      <c r="F7" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>55</v>
+      </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
-      <c r="H7" t="n">
-        <v>55</v>
-      </c>
+      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="L7" t="n">
+        <v>178</v>
+      </c>
+      <c r="M7" t="n">
+        <v>234</v>
+      </c>
+      <c r="N7" t="n">
+        <v>290</v>
+      </c>
       <c r="O7" t="n">
-        <v>242</v>
+        <v>702</v>
       </c>
       <c r="P7" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>547</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>26.3</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>26.83352340529355</v>
       </c>
       <c r="X7" t="n">
-        <v>19.8</v>
+        <v>26.18958080513761</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.28</v>
+        <v>1</v>
       </c>
       <c r="Z7" t="n">
-        <v>64.40000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>315.3</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>234</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>202</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>52069147</v>
+        <v>54966086</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -1306,71 +1291,77 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>65.55783709787821</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>82.2368240930869</v>
+      </c>
+      <c r="D8" t="n">
+        <v>22.77318640955</v>
+      </c>
       <c r="E8" t="n">
-        <v>33.9506172839506</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>30</v>
+      </c>
       <c r="G8" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" t="n">
-        <v>33</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="n">
-        <v>1</v>
-      </c>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="n">
+        <v>85</v>
+      </c>
+      <c r="M8" t="n">
+        <v>50</v>
+      </c>
+      <c r="N8" t="n">
+        <v>53</v>
+      </c>
       <c r="O8" t="n">
-        <v>70.09854</v>
+        <v>188</v>
       </c>
       <c r="P8" t="n">
-        <v>161.84105</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>295.33548</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>527.2751</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U8" t="n">
-        <v>128</v>
+        <v>21.5</v>
       </c>
       <c r="V8" t="n">
-        <v>128</v>
+        <v>0.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>22.09070610115507</v>
       </c>
       <c r="X8" t="n">
-        <v>29.530556</v>
+        <v>21.47480763832533</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.24</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
-        <v>95.23103</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>684.39825</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
@@ -1379,36 +1370,27 @@
         <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG8" t="n">
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>175</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>165</v>
+        <v>102</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>54192186</v>
+        <v>51630727</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -1416,74 +1398,86 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>83.6796714579055</v>
+        <v>93.4264202600958</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>19.330612244898</v>
       </c>
       <c r="E9" t="n">
-        <v>24.9739854318418</v>
+        <v>0</v>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="n">
+        <v>97</v>
+      </c>
+      <c r="I9" t="n">
+        <v>251</v>
+      </c>
       <c r="J9" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>135</v>
+      </c>
+      <c r="K9" t="n">
+        <v>483</v>
+      </c>
+      <c r="L9" t="n">
+        <v>91</v>
+      </c>
+      <c r="M9" t="n">
+        <v>245</v>
+      </c>
+      <c r="N9" t="n">
+        <v>135</v>
+      </c>
       <c r="O9" t="n">
-        <v>145</v>
+        <v>471</v>
       </c>
       <c r="P9" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>93</v>
+        <v>5</v>
       </c>
       <c r="R9" t="n">
-        <v>318</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>54</v>
+        <v>5</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>107</v>
+        <v>30.3</v>
       </c>
       <c r="V9" t="n">
-        <v>161</v>
+        <v>0.25</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>31.13070686877473</v>
       </c>
       <c r="X9" t="n">
-        <v>21.5</v>
+        <v>30.29860907292697</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.21</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>67</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>342.8</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
@@ -1492,33 +1486,24 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>233</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>164</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>142</v>
+        <v>120</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>51961920</v>
+        <v>53659629</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1526,84 +1511,88 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>85.864476386037</v>
+        <v>90.0232717316906</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>27.3796646836128</v>
       </c>
       <c r="E10" t="n">
-        <v>23.5555555555556</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>514</v>
+      </c>
+      <c r="I10" t="n">
+        <v>310</v>
+      </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="K10" t="n">
-        <v>456</v>
+        <v>862</v>
       </c>
       <c r="L10" t="n">
-        <v>379</v>
+        <v>500</v>
       </c>
       <c r="M10" t="n">
-        <v>506</v>
+        <v>131</v>
       </c>
       <c r="N10" t="n">
-        <v>1341</v>
+        <v>29</v>
       </c>
       <c r="O10" t="n">
-        <v>392</v>
+        <v>660</v>
       </c>
       <c r="P10" t="n">
-        <v>352</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>506</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1250</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>571</v>
+        <v>26</v>
       </c>
       <c r="V10" t="n">
-        <v>571</v>
+        <v>0.16</v>
       </c>
       <c r="W10" t="n">
-        <v>2</v>
+        <v>26.35605857601787</v>
       </c>
       <c r="X10" t="n">
-        <v>26.8</v>
+        <v>25.86180064978812</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.29</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>85</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>534.4</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1612,29 +1601,24 @@
         <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI10" t="n">
         <v>0</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>171</v>
       </c>
       <c r="AK10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
+        <v>192</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55311538</v>
+        <v>54964923</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -1642,80 +1626,86 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>85.5304585900068</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>82.52703627652291</v>
+      </c>
+      <c r="D11" t="n">
+        <v>30.8539944903581</v>
+      </c>
       <c r="E11" t="n">
-        <v>29.0532879818594</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>55</v>
+      </c>
       <c r="G11" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" t="n">
-        <v>65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="n">
-        <v>0</v>
-      </c>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="L11" t="n">
+        <v>486</v>
+      </c>
+      <c r="M11" t="n">
+        <v>276</v>
+      </c>
+      <c r="N11" t="n">
+        <v>322</v>
+      </c>
       <c r="O11" t="n">
-        <v>427</v>
+        <v>1084</v>
       </c>
       <c r="P11" t="n">
-        <v>200</v>
+        <v>6</v>
       </c>
       <c r="Q11" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>794</v>
+        <v>27</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U11" t="n">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="V11" t="n">
-        <v>12</v>
+        <v>0.19</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>25.01915705404594</v>
       </c>
       <c r="X11" t="n">
-        <v>22.9</v>
+        <v>24.60021860904132</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.36</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>71.09999999999999</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>352.6</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
         <v>0</v>
@@ -1724,27 +1714,18 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="AK11" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>104</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>51212898</v>
+        <v>52925856</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -1752,87 +1733,91 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>70.8966461327858</v>
+        <v>81.8261464750171</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>33.5180055401662</v>
       </c>
       <c r="E12" t="n">
-        <v>27.7388544139095</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="G12" t="n">
         <v>1</v>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>512</v>
+      </c>
+      <c r="I12" t="n">
+        <v>739</v>
+      </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>480</v>
       </c>
       <c r="K12" t="n">
-        <v>943</v>
+        <v>1731</v>
       </c>
       <c r="L12" t="n">
-        <v>899</v>
+        <v>435</v>
       </c>
       <c r="M12" t="n">
-        <v>860</v>
+        <v>739</v>
       </c>
       <c r="N12" t="n">
-        <v>2702</v>
+        <v>406</v>
       </c>
       <c r="O12" t="n">
-        <v>781</v>
+        <v>1580</v>
       </c>
       <c r="P12" t="n">
-        <v>894</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>843</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2518</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>227</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>70</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>32.4</v>
       </c>
       <c r="V12" t="n">
-        <v>297</v>
+        <v>0.17</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>33.13605915173261</v>
       </c>
       <c r="X12" t="n">
-        <v>25.4</v>
+        <v>32.35321050107357</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>501.6</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
@@ -1847,20 +1832,15 @@
         <v>0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>218</v>
       </c>
       <c r="AK12" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
+        <v>164</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>54706570</v>
+        <v>54177281</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1868,74 +1848,80 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>88.2299794661191</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>80.4517453798768</v>
+      </c>
+      <c r="D13" t="n">
+        <v>35.323147647377</v>
+      </c>
       <c r="E13" t="n">
-        <v>21.9713358572201</v>
-      </c>
-      <c r="F13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F13" t="n">
+        <v>60</v>
+      </c>
       <c r="G13" t="n">
         <v>0</v>
       </c>
-      <c r="H13" t="n">
-        <v>56</v>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="n">
-        <v>0</v>
-      </c>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="L13" t="n">
+        <v>385</v>
+      </c>
+      <c r="M13" t="n">
+        <v>91</v>
+      </c>
+      <c r="N13" t="n">
+        <v>95</v>
+      </c>
       <c r="O13" t="n">
-        <v>471</v>
+        <v>571</v>
       </c>
       <c r="P13" t="n">
-        <v>310</v>
+        <v>86</v>
       </c>
       <c r="Q13" t="n">
-        <v>184</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>964</v>
+        <v>4</v>
       </c>
       <c r="S13" t="n">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="V13" t="n">
-        <v>52</v>
+        <v>0.26</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>25.87859374674218</v>
       </c>
       <c r="X13" t="n">
-        <v>24.7</v>
+        <v>24.27458055875391</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>77.8</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>467.5</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -1944,33 +1930,24 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="AK13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM13" t="n">
-        <v>109</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>150</v>
+        <v>93</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>51619206</v>
+        <v>53982483</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1978,73 +1955,71 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>85.9794661190965</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>83.37303216974681</v>
+      </c>
+      <c r="D14" t="n">
+        <v>24.7720967102656</v>
+      </c>
       <c r="E14" t="n">
-        <v>22.4058769513315</v>
-      </c>
-      <c r="F14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="F14" t="n">
+        <v>31</v>
+      </c>
       <c r="G14" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="n">
-        <v>52</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="n">
-        <v>1</v>
-      </c>
-      <c r="K14" t="n">
-        <v>642</v>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="n">
-        <v>850</v>
+        <v>56</v>
       </c>
       <c r="M14" t="n">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="N14" t="n">
-        <v>1683</v>
+        <v>60</v>
       </c>
       <c r="O14" t="n">
-        <v>331</v>
+        <v>296</v>
       </c>
       <c r="P14" t="n">
-        <v>426</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>888</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>25.6</v>
       </c>
       <c r="V14" t="n">
-        <v>32</v>
+        <v>0.26</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>25.68760781503191</v>
       </c>
       <c r="X14" t="n">
-        <v>31.8</v>
+        <v>25.2187064020979</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.24</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>102.8</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>776.3</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2062,29 +2037,20 @@
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI14" t="n">
         <v>0</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>51180546</v>
+        <v>54904200</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -2092,109 +2058,102 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>83.9452429842574</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>80.87337440109511</v>
+      </c>
+      <c r="D15" t="n">
+        <v>25.1807851239669</v>
+      </c>
       <c r="E15" t="n">
-        <v>25.3443526170799</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>45</v>
+      </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
-      <c r="H15" t="n">
-        <v>72</v>
-      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="n">
-        <v>1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>238</v>
-      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="n">
-        <v>178</v>
+        <v>451</v>
       </c>
       <c r="M15" t="n">
-        <v>110</v>
+        <v>149</v>
       </c>
       <c r="N15" t="n">
-        <v>526</v>
+        <v>132</v>
       </c>
       <c r="O15" t="n">
-        <v>210</v>
+        <v>732</v>
       </c>
       <c r="P15" t="n">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>102</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>402</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U15" t="n">
-        <v>43</v>
+        <v>25.7</v>
       </c>
       <c r="V15" t="n">
-        <v>43</v>
+        <v>0.24</v>
       </c>
       <c r="W15" t="n">
-        <v>2</v>
+        <v>26.29239659878111</v>
       </c>
       <c r="X15" t="n">
-        <v>23</v>
+        <v>25.55473659607285</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>73</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>410.8</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI15" t="n">
         <v>0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>204</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL15" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
+        <v>154</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
